--- a/events_data.xlsx
+++ b/events_data.xlsx
@@ -1,67 +1,199 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Studies\BachelorY3\Sem1\Intern\registration\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F253F66D-B725-4E00-9DDE-C21E0A19E754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Add Events" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="How to Add Events" sheetId="2" r:id="rId1"/>
+    <sheet name="Events" sheetId="1" r:id="rId2"/>
+    <sheet name="Annual" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Registrations</t>
+  </si>
+  <si>
+    <t>Design for Change – Figma Workshop</t>
+  </si>
+  <si>
+    <t>Design for Change – Adobe Express Workshop</t>
+  </si>
+  <si>
+    <t>Design for Change – How to Pitch</t>
+  </si>
+  <si>
+    <t>Stepping into Industry</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>HOW TO ADD A NEW EVENT</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Go to the 'Events' sheet (tab at the bottom)</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Click on the next empty row after the last event</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Column A: Type the date as DD/MM/YYYY</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Column B: Type the event name</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Column C: Type the number of registrations</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Save the file (Ctrl+S)</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>The dashboard will update automatically when you reload it</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Start Talking Registrations</t>
+  </si>
+  <si>
+    <t>Start Talking Satisfaction</t>
+  </si>
+  <si>
+    <t>Design for Change Registrations</t>
+  </si>
+  <si>
+    <t>Design for Change Satisfaction</t>
+  </si>
+  <si>
+    <t>Combined Total</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Arial"/>
-      <b val="1"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002D7A5F"/>
+        <fgColor rgb="FF2D7A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F7F4"/>
+        <fgColor rgb="FFF0F7F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,106 +207,54 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -462,97 +542,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Registrations</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>45736</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Design for Change – Figma Workshop</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>45757</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Design for Change – Adobe Express Workshop</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Design for Change – How to Pitch</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>45917</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Stepping into Industry</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C6" s="6">
-        <f>SUM(C2:C5)</f>
-        <v/>
+      <c r="B9" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -561,127 +630,217 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>HOW TO ADD A NEW EVENT</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr"/>
-      <c r="B2" s="7" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Go to the 'Events' sheet (tab at the bottom)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Click on the next empty row after the last event</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Column A: Type the date as DD/MM/YYYY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Column B: Type the event name</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Column C: Type the number of registrations</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Save the file (Ctrl+S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>The dashboard will update automatically when you reload it</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>45736</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>45757</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>45778</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="6">
+        <f>SUM(C2:C5)</f>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13BE726-F896-4365-A2FD-DAA725E5AF15}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="8">
+        <v>153</v>
+      </c>
+      <c r="C2" s="8">
+        <v>80</v>
+      </c>
+      <c r="D2" s="8">
+        <v>96</v>
+      </c>
+      <c r="E2" s="8">
+        <v>83</v>
+      </c>
+      <c r="F2" s="8">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>2022</v>
+      </c>
+      <c r="B3" s="8">
+        <v>124</v>
+      </c>
+      <c r="C3" s="8">
+        <v>82</v>
+      </c>
+      <c r="D3" s="8">
+        <v>98</v>
+      </c>
+      <c r="E3" s="8">
+        <v>85</v>
+      </c>
+      <c r="F3" s="8">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B4" s="8">
+        <v>80</v>
+      </c>
+      <c r="C4" s="8">
+        <v>85</v>
+      </c>
+      <c r="D4" s="8">
+        <v>71</v>
+      </c>
+      <c r="E4" s="8">
+        <v>86</v>
+      </c>
+      <c r="F4" s="8">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="8">
+        <v>103</v>
+      </c>
+      <c r="C5" s="8">
+        <v>88</v>
+      </c>
+      <c r="D5" s="8">
+        <v>104</v>
+      </c>
+      <c r="E5" s="8">
+        <v>88</v>
+      </c>
+      <c r="F5" s="8">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="8">
+        <v>230</v>
+      </c>
+      <c r="C6" s="8">
+        <v>85</v>
+      </c>
+      <c r="D6" s="8">
+        <v>126</v>
+      </c>
+      <c r="E6" s="8">
+        <v>90</v>
+      </c>
+      <c r="F6" s="8">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/events_data.xlsx
+++ b/events_data.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Studies\BachelorY3\Sem1\Intern\registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F253F66D-B725-4E00-9DDE-C21E0A19E754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{F253F66D-B725-4E00-9DDE-C21E0A19E754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{838F6C2A-CD22-4FCC-A4C5-D59AEF65F418}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to Add Events" sheetId="2" r:id="rId1"/>
     <sheet name="Events" sheetId="1" r:id="rId2"/>
     <sheet name="Annual" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,6 +40,57 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
+    <t>HOW TO ADD A NEW EVENT</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Go to the 'Events' sheet (tab at the bottom)</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Click on the next empty row after the last event</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Column A: Type the date as DD/MM/YYYY</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Column B: Type the event name</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Column C: Type the number of registrations</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Save the file (Ctrl+S)</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>The dashboard will update automatically when you reload it</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -59,57 +113,6 @@
   </si>
   <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>HOW TO ADD A NEW EVENT</t>
-  </si>
-  <si>
-    <t>Step</t>
-  </si>
-  <si>
-    <t>Instruction</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Go to the 'Events' sheet (tab at the bottom)</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Click on the next empty row after the last event</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Column A: Type the date as DD/MM/YYYY</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Column B: Type the event name</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Column C: Type the number of registrations</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Save the file (Ctrl+S)</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>The dashboard will update automatically when you reload it</t>
   </si>
   <si>
     <t>Year</t>
@@ -135,9 +138,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,14 +227,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -240,6 +243,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,159 +550,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1" s="7"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B7" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B8" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B10" s="7" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;12&amp;K000000 Internal&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="2">
         <v>45736</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="4">
         <v>45757</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C3" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="2">
         <v>45778</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="4">
         <v>45917</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="B6" s="6" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C6" s="6">
         <f>SUM(C2:C5)</f>
@@ -705,22 +714,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;12&amp;K000000 Internal&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13BE726-F896-4365-A2FD-DAA725E5AF15}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="43.15">
       <c r="A1" s="9" t="s">
         <v>25</v>
       </c>
@@ -740,7 +752,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="8">
         <v>2021</v>
       </c>
@@ -760,7 +772,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="8">
         <v>2022</v>
       </c>
@@ -780,7 +792,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="15">
       <c r="A4" s="8">
         <v>2023</v>
       </c>
@@ -800,15 +812,15 @@
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="8">
         <v>2024</v>
       </c>
       <c r="B5" s="8">
         <v>103</v>
       </c>
-      <c r="C5" s="8">
-        <v>88</v>
+      <c r="C5" s="10">
+        <v>85</v>
       </c>
       <c r="D5" s="8">
         <v>104</v>
@@ -820,15 +832,15 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="15">
       <c r="A6" s="8">
         <v>2025</v>
       </c>
       <c r="B6" s="8">
         <v>230</v>
       </c>
-      <c r="C6" s="8">
-        <v>85</v>
+      <c r="C6" s="10">
+        <v>88</v>
       </c>
       <c r="D6" s="8">
         <v>126</v>
@@ -842,5 +854,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;12&amp;K000000 Internal&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5583b3fa-365b-4fa2-9885-a560b35483b3}" enabled="1" method="Standard" siteId="{df7f7579-3e9c-4a7e-b844-420280f53859}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/events_data.xlsx
+++ b/events_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Studies\BachelorY3\Sem1\Intern\registration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d79e2c508e5e5314/Desktop/Documents/GitHub/event_dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{F253F66D-B725-4E00-9DDE-C21E0A19E754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{838F6C2A-CD22-4FCC-A4C5-D59AEF65F418}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to Add Events" sheetId="2" r:id="rId1"/>
@@ -140,7 +140,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -550,23 +550,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -574,7 +574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
@@ -582,7 +582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
@@ -590,7 +590,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
@@ -598,7 +598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
@@ -606,7 +606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
@@ -614,7 +614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
@@ -622,7 +622,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
@@ -641,14 +641,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -659,7 +659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>45736</v>
       </c>
@@ -670,7 +670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>45757</v>
       </c>
@@ -681,7 +681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>45778</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>45917</v>
       </c>
@@ -703,7 +703,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" s="6" t="s">
         <v>24</v>
       </c>
@@ -723,16 +723,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13BE726-F896-4365-A2FD-DAA725E5AF15}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
+    <col min="5" max="5" width="17.7265625" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="43.15">
+    <row r="1" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>25</v>
       </c>
@@ -752,7 +752,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>2021</v>
       </c>
@@ -772,7 +772,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>2022</v>
       </c>
@@ -792,7 +792,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>2023</v>
       </c>
@@ -812,7 +812,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>2024</v>
       </c>
@@ -832,7 +832,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>2025</v>
       </c>
